--- a/gstdatabase/Settlement-of-IGST-to-State-2025-2026.xlsx
+++ b/gstdatabase/Settlement-of-IGST-to-State-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\Settlement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Mar-26\GST Statistics Downloads 31st Mar 26\Downloads\Settlement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E8E54C-DFC4-401F-ACF2-29BAE94B00E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248C884A-7634-40CF-A533-5DCE5DCA5602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
   <si>
     <t>Jammu and Kashmir</t>
   </si>
@@ -704,7 +704,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL45"/>
+  <dimension ref="A1:AO45"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -729,31 +729,32 @@
     <col min="37" max="37" width="12.21875" customWidth="1"/>
     <col min="38" max="38" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="11" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.6640625" customWidth="1"/>
+    <col min="41" max="41" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>40</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
-    <row r="2" spans="1:38" ht="23.1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:41" ht="23.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
         <v>47</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:38" ht="23.1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" ht="23.1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="19" t="s">
         <v>46</v>
       </c>
@@ -814,8 +815,13 @@
       </c>
       <c r="AK4" s="15"/>
       <c r="AL4" s="16"/>
+      <c r="AM4" s="14">
+        <v>46082</v>
+      </c>
+      <c r="AN4" s="15"/>
+      <c r="AO4" s="16"/>
     </row>
-    <row r="5" spans="1:38" ht="37.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" ht="37.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>39</v>
       </c>
@@ -930,8 +936,17 @@
       <c r="AL5" s="7" t="s">
         <v>43</v>
       </c>
+      <c r="AM5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO5" s="7" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -940,7 +955,7 @@
       </c>
       <c r="C6" s="8">
         <f>F6+I6+L6+O6+R6+U6+X6+AA6+AD6+AG6+AJ6+AM6</f>
-        <v>4904.1011919650009</v>
+        <v>5349.6364040335011</v>
       </c>
       <c r="D6" s="8">
         <f t="shared" ref="D6:E6" si="0">G6+J6+M6+P6+S6+V6+Y6+AB6+AE6+AH6+AK6+AN6</f>
@@ -948,7 +963,7 @@
       </c>
       <c r="E6" s="8">
         <f t="shared" si="0"/>
-        <v>4904.1011919650009</v>
+        <v>5349.6364040335011</v>
       </c>
       <c r="F6" s="9">
         <v>610.91604289599991</v>
@@ -1060,8 +1075,18 @@
         <f>AJ6+AK6</f>
         <v>395.15753668100007</v>
       </c>
+      <c r="AM6" s="9">
+        <v>445.53521206850002</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="9">
+        <f>AM6+AN6</f>
+        <v>445.53521206850002</v>
+      </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -1070,7 +1095,7 @@
       </c>
       <c r="C7" s="8">
         <f t="shared" ref="C7:C43" si="1">F7+I7+L7+O7+R7+U7+X7+AA7+AD7+AG7+AJ7+AM7</f>
-        <v>3608.0460654845006</v>
+        <v>3873.8607433350007</v>
       </c>
       <c r="D7" s="8">
         <f t="shared" ref="D7:D43" si="2">G7+J7+M7+P7+S7+V7+Y7+AB7+AE7+AH7+AK7+AN7</f>
@@ -1078,7 +1103,7 @@
       </c>
       <c r="E7" s="8">
         <f t="shared" ref="E7:E43" si="3">H7+K7+N7+Q7+T7+W7+Z7+AC7+AF7+AI7+AL7+AO7</f>
-        <v>3608.0460654845006</v>
+        <v>3873.8607433350007</v>
       </c>
       <c r="F7" s="9">
         <v>431.22853366000004</v>
@@ -1190,8 +1215,18 @@
         <f t="shared" ref="AL7:AL43" si="14">AJ7+AK7</f>
         <v>332.27075286450003</v>
       </c>
+      <c r="AM7" s="9">
+        <v>265.8146778505</v>
+      </c>
+      <c r="AN7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="9">
+        <f t="shared" ref="AO7:AO43" si="15">AM7+AN7</f>
+        <v>265.8146778505</v>
+      </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -1200,7 +1235,7 @@
       </c>
       <c r="C8" s="8">
         <f t="shared" si="1"/>
-        <v>16406.927051874496</v>
+        <v>17874.650070233994</v>
       </c>
       <c r="D8" s="8">
         <f t="shared" si="2"/>
@@ -1208,7 +1243,7 @@
       </c>
       <c r="E8" s="8">
         <f t="shared" si="3"/>
-        <v>16406.927051874496</v>
+        <v>17874.650070233994</v>
       </c>
       <c r="F8" s="9">
         <v>1571.3228304389997</v>
@@ -1320,8 +1355,18 @@
         <f t="shared" si="14"/>
         <v>1520.8007471170004</v>
       </c>
+      <c r="AM8" s="9">
+        <v>1467.7230183595</v>
+      </c>
+      <c r="AN8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="9">
+        <f t="shared" si="15"/>
+        <v>1467.7230183595</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -1330,7 +1375,7 @@
       </c>
       <c r="C9" s="8">
         <f t="shared" si="1"/>
-        <v>1601.5850351154997</v>
+        <v>1739.5175059509997</v>
       </c>
       <c r="D9" s="8">
         <f t="shared" si="2"/>
@@ -1338,7 +1383,7 @@
       </c>
       <c r="E9" s="8">
         <f t="shared" si="3"/>
-        <v>1601.5850351154997</v>
+        <v>1739.5175059509997</v>
       </c>
       <c r="F9" s="9">
         <v>179.76297837400003</v>
@@ -1450,8 +1495,18 @@
         <f t="shared" si="14"/>
         <v>142.7245876035</v>
       </c>
+      <c r="AM9" s="9">
+        <v>137.9324708355</v>
+      </c>
+      <c r="AN9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="9">
+        <f t="shared" si="15"/>
+        <v>137.9324708355</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -1460,7 +1515,7 @@
       </c>
       <c r="C10" s="8">
         <f t="shared" si="1"/>
-        <v>4021.7140542569996</v>
+        <v>4455.5051970239992</v>
       </c>
       <c r="D10" s="8">
         <f t="shared" si="2"/>
@@ -1468,7 +1523,7 @@
       </c>
       <c r="E10" s="8">
         <f t="shared" si="3"/>
-        <v>4021.7140542569996</v>
+        <v>4455.5051970239992</v>
       </c>
       <c r="F10" s="9">
         <v>447.64504802400006</v>
@@ -1580,8 +1635,18 @@
         <f t="shared" si="14"/>
         <v>373.02067506700001</v>
       </c>
+      <c r="AM10" s="9">
+        <v>433.791142767</v>
+      </c>
+      <c r="AN10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="9">
+        <f t="shared" si="15"/>
+        <v>433.791142767</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>6</v>
       </c>
@@ -1590,7 +1655,7 @@
       </c>
       <c r="C11" s="8">
         <f t="shared" si="1"/>
-        <v>22659.912426228497</v>
+        <v>24447.987488823499</v>
       </c>
       <c r="D11" s="8">
         <f t="shared" si="2"/>
@@ -1598,7 +1663,7 @@
       </c>
       <c r="E11" s="8">
         <f t="shared" si="3"/>
-        <v>22659.912426228497</v>
+        <v>24447.987488823499</v>
       </c>
       <c r="F11" s="9">
         <v>2097.8142966089999</v>
@@ -1710,8 +1775,18 @@
         <f t="shared" si="14"/>
         <v>2377.7183604420002</v>
       </c>
+      <c r="AM11" s="9">
+        <v>1788.0750625950004</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="9">
+        <f t="shared" si="15"/>
+        <v>1788.0750625950004</v>
+      </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>7</v>
       </c>
@@ -1720,7 +1795,7 @@
       </c>
       <c r="C12" s="8">
         <f t="shared" si="1"/>
-        <v>17838.268651232502</v>
+        <v>19159.750628591002</v>
       </c>
       <c r="D12" s="8">
         <f t="shared" si="2"/>
@@ -1728,7 +1803,7 @@
       </c>
       <c r="E12" s="8">
         <f t="shared" si="3"/>
-        <v>17838.268651232502</v>
+        <v>19159.750628591002</v>
       </c>
       <c r="F12" s="9">
         <v>2061.8576271830002</v>
@@ -1840,8 +1915,18 @@
         <f t="shared" si="14"/>
         <v>1552.1704524649997</v>
       </c>
+      <c r="AM12" s="9">
+        <v>1321.4819773585</v>
+      </c>
+      <c r="AN12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="9">
+        <f t="shared" si="15"/>
+        <v>1321.4819773585</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>8</v>
       </c>
@@ -1850,7 +1935,7 @@
       </c>
       <c r="C13" s="8">
         <f t="shared" si="1"/>
-        <v>25188.596583890005</v>
+        <v>27449.996849599003</v>
       </c>
       <c r="D13" s="8">
         <f t="shared" si="2"/>
@@ -1858,7 +1943,7 @@
       </c>
       <c r="E13" s="8">
         <f t="shared" si="3"/>
-        <v>25188.596583890005</v>
+        <v>27449.996849599003</v>
       </c>
       <c r="F13" s="9">
         <v>2655.2886687270002</v>
@@ -1970,8 +2055,18 @@
         <f t="shared" si="14"/>
         <v>2260.9374276205008</v>
       </c>
+      <c r="AM13" s="9">
+        <v>2261.400265709</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="9">
+        <f t="shared" si="15"/>
+        <v>2261.400265709</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>9</v>
       </c>
@@ -1980,7 +2075,7 @@
       </c>
       <c r="C14" s="8">
         <f t="shared" si="1"/>
-        <v>47235.998239977002</v>
+        <v>51421.572738886003</v>
       </c>
       <c r="D14" s="8">
         <f t="shared" si="2"/>
@@ -1988,7 +2083,7 @@
       </c>
       <c r="E14" s="8">
         <f t="shared" si="3"/>
-        <v>47235.998239977002</v>
+        <v>51421.572738886003</v>
       </c>
       <c r="F14" s="9">
         <v>4877.5089042420004</v>
@@ -2100,8 +2195,18 @@
         <f t="shared" si="14"/>
         <v>4593.0468136615009</v>
       </c>
+      <c r="AM14" s="9">
+        <v>4185.5744989090008</v>
+      </c>
+      <c r="AN14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="9">
+        <f t="shared" si="15"/>
+        <v>4185.5744989090008</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>10</v>
       </c>
@@ -2110,7 +2215,7 @@
       </c>
       <c r="C15" s="8">
         <f t="shared" si="1"/>
-        <v>19643.245106585004</v>
+        <v>21573.287697516505</v>
       </c>
       <c r="D15" s="8">
         <f t="shared" si="2"/>
@@ -2118,7 +2223,7 @@
       </c>
       <c r="E15" s="8">
         <f t="shared" si="3"/>
-        <v>19643.245106585004</v>
+        <v>21573.287697516505</v>
       </c>
       <c r="F15" s="9">
         <v>1998.3971381449996</v>
@@ -2230,8 +2335,18 @@
         <f t="shared" si="14"/>
         <v>1760.285198261</v>
       </c>
+      <c r="AM15" s="9">
+        <v>1930.0425909314999</v>
+      </c>
+      <c r="AN15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="9">
+        <f t="shared" si="15"/>
+        <v>1930.0425909314999</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>11</v>
       </c>
@@ -2240,7 +2355,7 @@
       </c>
       <c r="C16" s="8">
         <f t="shared" si="1"/>
-        <v>615.50635557800001</v>
+        <v>672.0674066885</v>
       </c>
       <c r="D16" s="8">
         <f t="shared" si="2"/>
@@ -2248,7 +2363,7 @@
       </c>
       <c r="E16" s="8">
         <f t="shared" si="3"/>
-        <v>615.50635557800001</v>
+        <v>672.0674066885</v>
       </c>
       <c r="F16" s="9">
         <v>79.491136306999991</v>
@@ -2360,8 +2475,18 @@
         <f t="shared" si="14"/>
         <v>48.532287841500001</v>
       </c>
+      <c r="AM16" s="9">
+        <v>56.561051110500003</v>
+      </c>
+      <c r="AN16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="9">
+        <f t="shared" si="15"/>
+        <v>56.561051110500003</v>
+      </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>12</v>
       </c>
@@ -2370,7 +2495,7 @@
       </c>
       <c r="C17" s="8">
         <f t="shared" si="1"/>
-        <v>1185.107994983</v>
+        <v>1297.0993055085</v>
       </c>
       <c r="D17" s="8">
         <f t="shared" si="2"/>
@@ -2378,7 +2503,7 @@
       </c>
       <c r="E17" s="8">
         <f t="shared" si="3"/>
-        <v>1185.107994983</v>
+        <v>1297.0993055085</v>
       </c>
       <c r="F17" s="9">
         <v>163.89321527199999</v>
@@ -2490,8 +2615,18 @@
         <f t="shared" si="14"/>
         <v>100.16773821250001</v>
       </c>
+      <c r="AM17" s="9">
+        <v>111.99131052550001</v>
+      </c>
+      <c r="AN17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="9">
+        <f t="shared" si="15"/>
+        <v>111.99131052550001</v>
+      </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>13</v>
       </c>
@@ -2500,7 +2635,7 @@
       </c>
       <c r="C18" s="8">
         <f t="shared" si="1"/>
-        <v>744.625907869</v>
+        <v>810.89103688599994</v>
       </c>
       <c r="D18" s="8">
         <f t="shared" si="2"/>
@@ -2508,7 +2643,7 @@
       </c>
       <c r="E18" s="8">
         <f t="shared" si="3"/>
-        <v>744.625907869</v>
+        <v>810.89103688599994</v>
       </c>
       <c r="F18" s="9">
         <v>94.159376584</v>
@@ -2620,8 +2755,18 @@
         <f t="shared" si="14"/>
         <v>62.628616636499999</v>
       </c>
+      <c r="AM18" s="9">
+        <v>66.265129016999992</v>
+      </c>
+      <c r="AN18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="9">
+        <f t="shared" si="15"/>
+        <v>66.265129016999992</v>
+      </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>14</v>
       </c>
@@ -2630,7 +2775,7 @@
       </c>
       <c r="C19" s="8">
         <f t="shared" si="1"/>
-        <v>751.02640003199986</v>
+        <v>829.20472191249985</v>
       </c>
       <c r="D19" s="8">
         <f t="shared" si="2"/>
@@ -2638,7 +2783,7 @@
       </c>
       <c r="E19" s="8">
         <f t="shared" si="3"/>
-        <v>751.02640003199986</v>
+        <v>829.20472191249985</v>
       </c>
       <c r="F19" s="9">
         <v>63.435431519999995</v>
@@ -2750,8 +2895,18 @@
         <f t="shared" si="14"/>
         <v>70.374299580499994</v>
       </c>
+      <c r="AM19" s="9">
+        <v>78.178321880499979</v>
+      </c>
+      <c r="AN19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="9">
+        <f t="shared" si="15"/>
+        <v>78.178321880499979</v>
+      </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>15</v>
       </c>
@@ -2760,7 +2915,7 @@
       </c>
       <c r="C20" s="8">
         <f t="shared" si="1"/>
-        <v>659.57188306300009</v>
+        <v>720.02306672650013</v>
       </c>
       <c r="D20" s="8">
         <f t="shared" si="2"/>
@@ -2768,7 +2923,7 @@
       </c>
       <c r="E20" s="8">
         <f t="shared" si="3"/>
-        <v>659.57188306300009</v>
+        <v>720.02306672650013</v>
       </c>
       <c r="F20" s="9">
         <v>72.995567592000015</v>
@@ -2880,8 +3035,18 @@
         <f t="shared" si="14"/>
         <v>63.320738088999995</v>
       </c>
+      <c r="AM20" s="9">
+        <v>60.451183663499997</v>
+      </c>
+      <c r="AN20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="9">
+        <f t="shared" si="15"/>
+        <v>60.451183663499997</v>
+      </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>16</v>
       </c>
@@ -2890,7 +3055,7 @@
       </c>
       <c r="C21" s="8">
         <f t="shared" si="1"/>
-        <v>1022.5331961625</v>
+        <v>1103.3060584575001</v>
       </c>
       <c r="D21" s="8">
         <f t="shared" si="2"/>
@@ -2898,7 +3063,7 @@
       </c>
       <c r="E21" s="8">
         <f t="shared" si="3"/>
-        <v>1022.5331961625</v>
+        <v>1103.3060584575001</v>
       </c>
       <c r="F21" s="9">
         <v>124.29654346299999</v>
@@ -3010,8 +3175,18 @@
         <f t="shared" si="14"/>
         <v>81.586718187000017</v>
       </c>
+      <c r="AM21" s="9">
+        <v>80.772862294999996</v>
+      </c>
+      <c r="AN21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="9">
+        <f t="shared" si="15"/>
+        <v>80.772862294999996</v>
+      </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>17</v>
       </c>
@@ -3020,7 +3195,7 @@
       </c>
       <c r="C22" s="8">
         <f t="shared" si="1"/>
-        <v>1035.7487112765</v>
+        <v>1125.3551211204999</v>
       </c>
       <c r="D22" s="8">
         <f t="shared" si="2"/>
@@ -3028,7 +3203,7 @@
       </c>
       <c r="E22" s="8">
         <f t="shared" si="3"/>
-        <v>1035.7487112765</v>
+        <v>1125.3551211204999</v>
       </c>
       <c r="F22" s="9">
         <v>114.67371064700001</v>
@@ -3140,8 +3315,18 @@
         <f t="shared" si="14"/>
         <v>95.453066590000006</v>
       </c>
+      <c r="AM22" s="9">
+        <v>89.606409844000012</v>
+      </c>
+      <c r="AN22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="9">
+        <f t="shared" si="15"/>
+        <v>89.606409844000012</v>
+      </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>18</v>
       </c>
@@ -3150,7 +3335,7 @@
       </c>
       <c r="C23" s="8">
         <f t="shared" si="1"/>
-        <v>10578.991125386499</v>
+        <v>11343.026657188999</v>
       </c>
       <c r="D23" s="8">
         <f t="shared" si="2"/>
@@ -3158,7 +3343,7 @@
       </c>
       <c r="E23" s="8">
         <f t="shared" si="3"/>
-        <v>10578.991125386499</v>
+        <v>11343.026657188999</v>
       </c>
       <c r="F23" s="12">
         <v>858.96011183299993</v>
@@ -3270,8 +3455,18 @@
         <f t="shared" si="14"/>
         <v>764.2933247970002</v>
       </c>
+      <c r="AM23" s="9">
+        <v>764.03553180249992</v>
+      </c>
+      <c r="AN23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="12">
+        <f t="shared" si="15"/>
+        <v>764.03553180249992</v>
+      </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>19</v>
       </c>
@@ -3280,7 +3475,7 @@
       </c>
       <c r="C24" s="8">
         <f t="shared" si="1"/>
-        <v>21367.751690930498</v>
+        <v>23010.190421119998</v>
       </c>
       <c r="D24" s="8">
         <f t="shared" si="2"/>
@@ -3288,7 +3483,7 @@
       </c>
       <c r="E24" s="8">
         <f t="shared" si="3"/>
-        <v>21367.751690930498</v>
+        <v>23010.190421119998</v>
       </c>
       <c r="F24" s="9">
         <v>2195.5006374370005</v>
@@ -3400,8 +3595,18 @@
         <f t="shared" si="14"/>
         <v>1839.2011411134999</v>
       </c>
+      <c r="AM24" s="9">
+        <v>1642.4387301895003</v>
+      </c>
+      <c r="AN24" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="9">
+        <f t="shared" si="15"/>
+        <v>1642.4387301895003</v>
+      </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>20</v>
       </c>
@@ -3410,7 +3615,7 @@
       </c>
       <c r="C25" s="8">
         <f t="shared" si="1"/>
-        <v>3457.6752452939995</v>
+        <v>3258.6621304464998</v>
       </c>
       <c r="D25" s="8">
         <f t="shared" si="2"/>
@@ -3418,7 +3623,7 @@
       </c>
       <c r="E25" s="8">
         <f t="shared" si="3"/>
-        <v>3457.6752452939995</v>
+        <v>3258.6621304464998</v>
       </c>
       <c r="F25" s="9">
         <v>561.74262967599998</v>
@@ -3530,8 +3735,18 @@
         <f t="shared" si="14"/>
         <v>-92.302448296000065</v>
       </c>
+      <c r="AM25" s="9">
+        <v>-199.01311484749993</v>
+      </c>
+      <c r="AN25" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="9">
+        <f t="shared" si="15"/>
+        <v>-199.01311484749993</v>
+      </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>21</v>
       </c>
@@ -3540,7 +3755,7 @@
       </c>
       <c r="C26" s="8">
         <f t="shared" si="1"/>
-        <v>5330.5714153769995</v>
+        <v>5271.1326547279996</v>
       </c>
       <c r="D26" s="8">
         <f t="shared" si="2"/>
@@ -3548,7 +3763,7 @@
       </c>
       <c r="E26" s="8">
         <f t="shared" si="3"/>
-        <v>5330.5714153769995</v>
+        <v>5271.1326547279996</v>
       </c>
       <c r="F26" s="9">
         <v>962.28610711599981</v>
@@ -3660,8 +3875,18 @@
         <f t="shared" si="14"/>
         <v>136.10336739349992</v>
       </c>
+      <c r="AM26" s="9">
+        <v>-59.438760649000038</v>
+      </c>
+      <c r="AN26" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="9">
+        <f t="shared" si="15"/>
+        <v>-59.438760649000038</v>
+      </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>22</v>
       </c>
@@ -3670,7 +3895,7 @@
       </c>
       <c r="C27" s="8">
         <f t="shared" si="1"/>
-        <v>4918.0009654340001</v>
+        <v>5089.327393433</v>
       </c>
       <c r="D27" s="8">
         <f t="shared" si="2"/>
@@ -3678,7 +3903,7 @@
       </c>
       <c r="E27" s="8">
         <f t="shared" si="3"/>
-        <v>4918.0009654340001</v>
+        <v>5089.327393433</v>
       </c>
       <c r="F27" s="9">
         <v>570.23229198699994</v>
@@ -3790,8 +4015,18 @@
         <f t="shared" si="14"/>
         <v>348.02019044800011</v>
       </c>
+      <c r="AM27" s="9">
+        <v>171.32642799900006</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="9">
+        <f t="shared" si="15"/>
+        <v>171.32642799900006</v>
+      </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>23</v>
       </c>
@@ -3800,7 +4035,7 @@
       </c>
       <c r="C28" s="8">
         <f t="shared" si="1"/>
-        <v>19172.402267979498</v>
+        <v>20971.968226874997</v>
       </c>
       <c r="D28" s="8">
         <f t="shared" si="2"/>
@@ -3808,7 +4043,7 @@
       </c>
       <c r="E28" s="8">
         <f t="shared" si="3"/>
-        <v>19172.402267979498</v>
+        <v>20971.968226874997</v>
       </c>
       <c r="F28" s="9">
         <v>2326.5623952519995</v>
@@ -3920,8 +4155,18 @@
         <f t="shared" si="14"/>
         <v>1566.7639092620002</v>
       </c>
+      <c r="AM28" s="9">
+        <v>1799.5659588955002</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="9">
+        <f t="shared" si="15"/>
+        <v>1799.5659588955002</v>
+      </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>24</v>
       </c>
@@ -3930,7 +4175,7 @@
       </c>
       <c r="C29" s="8">
         <f t="shared" si="1"/>
-        <v>31582.581832861</v>
+        <v>33967.583625516498</v>
       </c>
       <c r="D29" s="8">
         <f t="shared" si="2"/>
@@ -3938,7 +4183,7 @@
       </c>
       <c r="E29" s="8">
         <f t="shared" si="3"/>
-        <v>31582.581832861</v>
+        <v>33967.583625516498</v>
       </c>
       <c r="F29" s="9">
         <v>3282.9994654389998</v>
@@ -4050,8 +4295,18 @@
         <f t="shared" si="14"/>
         <v>3322.2323868889994</v>
       </c>
+      <c r="AM29" s="9">
+        <v>2385.0017926555001</v>
+      </c>
+      <c r="AN29" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="9">
+        <f t="shared" si="15"/>
+        <v>2385.0017926555001</v>
+      </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>25</v>
       </c>
@@ -4060,7 +4315,7 @@
       </c>
       <c r="C30" s="8">
         <f t="shared" si="1"/>
-        <v>0.43035982</v>
+        <v>0.440320094</v>
       </c>
       <c r="D30" s="8">
         <f t="shared" si="2"/>
@@ -4068,7 +4323,7 @@
       </c>
       <c r="E30" s="8">
         <f t="shared" si="3"/>
-        <v>0.43035982</v>
+        <v>0.440320094</v>
       </c>
       <c r="F30" s="9">
         <v>4.6224979999999999E-2</v>
@@ -4180,8 +4435,18 @@
         <f t="shared" si="14"/>
         <v>2.0307663E-2</v>
       </c>
+      <c r="AM30" s="9">
+        <v>9.9602739999999999E-3</v>
+      </c>
+      <c r="AN30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="9">
+        <f t="shared" si="15"/>
+        <v>9.9602739999999999E-3</v>
+      </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>26</v>
       </c>
@@ -4190,7 +4455,7 @@
       </c>
       <c r="C31" s="8">
         <f t="shared" si="1"/>
-        <v>575.89892075299997</v>
+        <v>612.93822028699992</v>
       </c>
       <c r="D31" s="8">
         <f t="shared" si="2"/>
@@ -4198,7 +4463,7 @@
       </c>
       <c r="E31" s="8">
         <f t="shared" si="3"/>
-        <v>575.89892075299997</v>
+        <v>612.93822028699992</v>
       </c>
       <c r="F31" s="9">
         <v>51.840296495999993</v>
@@ -4310,8 +4575,18 @@
         <f t="shared" si="14"/>
         <v>92.617240735999971</v>
       </c>
+      <c r="AM31" s="9">
+        <v>37.039299533999994</v>
+      </c>
+      <c r="AN31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="9">
+        <f t="shared" si="15"/>
+        <v>37.039299533999994</v>
+      </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>27</v>
       </c>
@@ -4320,7 +4595,7 @@
       </c>
       <c r="C32" s="8">
         <f t="shared" si="1"/>
-        <v>70174.976960212487</v>
+        <v>75424.13825193599</v>
       </c>
       <c r="D32" s="8">
         <f t="shared" si="2"/>
@@ -4328,7 +4603,7 @@
       </c>
       <c r="E32" s="8">
         <f t="shared" si="3"/>
-        <v>70174.976960212487</v>
+        <v>75424.13825193599</v>
       </c>
       <c r="F32" s="9">
         <v>6723.8567862060008</v>
@@ -4440,8 +4715,18 @@
         <f t="shared" si="14"/>
         <v>6294.6394375995005</v>
       </c>
+      <c r="AM32" s="9">
+        <v>5249.1612917235025</v>
+      </c>
+      <c r="AN32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="9">
+        <f t="shared" si="15"/>
+        <v>5249.1612917235025</v>
+      </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>29</v>
       </c>
@@ -4450,7 +4735,7 @@
       </c>
       <c r="C33" s="8">
         <f t="shared" si="1"/>
-        <v>36526.58438557401</v>
+        <v>39345.199754328511</v>
       </c>
       <c r="D33" s="8">
         <f t="shared" si="2"/>
@@ -4458,7 +4743,7 @@
       </c>
       <c r="E33" s="8">
         <f t="shared" si="3"/>
-        <v>36526.58438557401</v>
+        <v>39345.199754328511</v>
       </c>
       <c r="F33" s="9">
         <v>3519.6222573769996</v>
@@ -4570,8 +4855,18 @@
         <f t="shared" si="14"/>
         <v>3707.6753541845001</v>
       </c>
+      <c r="AM33" s="9">
+        <v>2818.6153687545002</v>
+      </c>
+      <c r="AN33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="9">
+        <f t="shared" si="15"/>
+        <v>2818.6153687545002</v>
+      </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>30</v>
       </c>
@@ -4580,7 +4875,7 @@
       </c>
       <c r="C34" s="8">
         <f t="shared" si="1"/>
-        <v>1867.7323433279998</v>
+        <v>2021.1968263839999</v>
       </c>
       <c r="D34" s="8">
         <f t="shared" si="2"/>
@@ -4588,7 +4883,7 @@
       </c>
       <c r="E34" s="8">
         <f t="shared" si="3"/>
-        <v>1867.7323433279998</v>
+        <v>2021.1968263839999</v>
       </c>
       <c r="F34" s="9">
         <v>222.02109286500001</v>
@@ -4700,8 +4995,18 @@
         <f t="shared" si="14"/>
         <v>177.99369705399999</v>
       </c>
+      <c r="AM34" s="9">
+        <v>153.46448305600001</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="9">
+        <f t="shared" si="15"/>
+        <v>153.46448305600001</v>
+      </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>31</v>
       </c>
@@ -4710,7 +5015,7 @@
       </c>
       <c r="C35" s="8">
         <f t="shared" si="1"/>
-        <v>14.046889030000006</v>
+        <v>21.629441366000005</v>
       </c>
       <c r="D35" s="8">
         <f t="shared" si="2"/>
@@ -4718,7 +5023,7 @@
       </c>
       <c r="E35" s="8">
         <f t="shared" si="3"/>
-        <v>14.046889030000006</v>
+        <v>21.629441366000005</v>
       </c>
       <c r="F35" s="9">
         <v>10.197584595999999</v>
@@ -4830,8 +5135,18 @@
         <f t="shared" si="14"/>
         <v>8.698783370000001</v>
       </c>
+      <c r="AM35" s="9">
+        <v>7.5825523359999982</v>
+      </c>
+      <c r="AN35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="9">
+        <f t="shared" si="15"/>
+        <v>7.5825523359999982</v>
+      </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>32</v>
       </c>
@@ -4840,7 +5155,7 @@
       </c>
       <c r="C36" s="8">
         <f t="shared" si="1"/>
-        <v>17243.8488658075</v>
+        <v>18731.197105688501</v>
       </c>
       <c r="D36" s="8">
         <f t="shared" si="2"/>
@@ -4848,7 +5163,7 @@
       </c>
       <c r="E36" s="8">
         <f t="shared" si="3"/>
-        <v>17243.8488658075</v>
+        <v>18731.197105688501</v>
       </c>
       <c r="F36" s="9">
         <v>1700.565150185</v>
@@ -4960,8 +5275,18 @@
         <f t="shared" si="14"/>
         <v>1499.537585558</v>
       </c>
+      <c r="AM36" s="9">
+        <v>1487.3482398810002</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="9">
+        <f t="shared" si="15"/>
+        <v>1487.3482398810002</v>
+      </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>33</v>
       </c>
@@ -4970,7 +5295,7 @@
       </c>
       <c r="C37" s="8">
         <f t="shared" si="1"/>
-        <v>29741.034670823505</v>
+        <v>32428.288516666504</v>
       </c>
       <c r="D37" s="8">
         <f t="shared" si="2"/>
@@ -4978,7 +5303,7 @@
       </c>
       <c r="E37" s="8">
         <f t="shared" si="3"/>
-        <v>29741.034670823505</v>
+        <v>32428.288516666504</v>
       </c>
       <c r="F37" s="9">
         <v>2635.5875665139997</v>
@@ -5090,8 +5415,18 @@
         <f t="shared" si="14"/>
         <v>3097.9217103014998</v>
       </c>
+      <c r="AM37" s="9">
+        <v>2687.2538458429995</v>
+      </c>
+      <c r="AN37" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="9">
+        <f t="shared" si="15"/>
+        <v>2687.2538458429995</v>
+      </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>34</v>
       </c>
@@ -5100,7 +5435,7 @@
       </c>
       <c r="C38" s="8">
         <f t="shared" si="1"/>
-        <v>846.70070766349988</v>
+        <v>929.57478301549986</v>
       </c>
       <c r="D38" s="8">
         <f t="shared" si="2"/>
@@ -5108,7 +5443,7 @@
       </c>
       <c r="E38" s="8">
         <f t="shared" si="3"/>
-        <v>846.70070766349988</v>
+        <v>929.57478301549986</v>
       </c>
       <c r="F38" s="9">
         <v>80.09905869100001</v>
@@ -5220,8 +5555,18 @@
         <f t="shared" si="14"/>
         <v>79.124573287999993</v>
       </c>
+      <c r="AM38" s="9">
+        <v>82.874075351999991</v>
+      </c>
+      <c r="AN38" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="9">
+        <f t="shared" si="15"/>
+        <v>82.874075351999991</v>
+      </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>35</v>
       </c>
@@ -5230,7 +5575,7 @@
       </c>
       <c r="C39" s="8">
         <f t="shared" si="1"/>
-        <v>456.73860090249997</v>
+        <v>492.97926428849996</v>
       </c>
       <c r="D39" s="8">
         <f t="shared" si="2"/>
@@ -5238,7 +5583,7 @@
       </c>
       <c r="E39" s="8">
         <f t="shared" si="3"/>
-        <v>456.73860090249997</v>
+        <v>492.97926428849996</v>
       </c>
       <c r="F39" s="9">
         <v>59.646514219999993</v>
@@ -5350,8 +5695,18 @@
         <f t="shared" si="14"/>
         <v>32.850707196999998</v>
       </c>
+      <c r="AM39" s="9">
+        <v>36.240663385999994</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="9">
+        <f t="shared" si="15"/>
+        <v>36.240663385999994</v>
+      </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>36</v>
       </c>
@@ -5360,7 +5715,7 @@
       </c>
       <c r="C40" s="8">
         <f t="shared" si="1"/>
-        <v>22696.283985155504</v>
+        <v>24548.069618820002</v>
       </c>
       <c r="D40" s="8">
         <f t="shared" si="2"/>
@@ -5368,7 +5723,7 @@
       </c>
       <c r="E40" s="8">
         <f t="shared" si="3"/>
-        <v>22696.283985155504</v>
+        <v>24548.069618820002</v>
       </c>
       <c r="F40" s="9">
         <v>2289.7651787750001</v>
@@ -5480,8 +5835,18 @@
         <f t="shared" si="14"/>
         <v>2166.4363905390001</v>
       </c>
+      <c r="AM40" s="9">
+        <v>1851.7856336645</v>
+      </c>
+      <c r="AN40" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO40" s="9">
+        <f t="shared" si="15"/>
+        <v>1851.7856336645</v>
+      </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>37</v>
       </c>
@@ -5490,7 +5855,7 @@
       </c>
       <c r="C41" s="8">
         <f t="shared" si="1"/>
-        <v>18312.686206466497</v>
+        <v>20019.448194644996</v>
       </c>
       <c r="D41" s="8">
         <f t="shared" si="2"/>
@@ -5498,7 +5863,7 @@
       </c>
       <c r="E41" s="8">
         <f t="shared" si="3"/>
-        <v>18312.686206466497</v>
+        <v>20019.448194644996</v>
       </c>
       <c r="F41" s="9">
         <v>1942.8355840589995</v>
@@ -5610,8 +5975,18 @@
         <f t="shared" si="14"/>
         <v>1809.8583755049999</v>
       </c>
+      <c r="AM41" s="9">
+        <v>1706.7619881785001</v>
+      </c>
+      <c r="AN41" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO41" s="9">
+        <f t="shared" si="15"/>
+        <v>1706.7619881785001</v>
+      </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>38</v>
       </c>
@@ -5620,7 +5995,7 @@
       </c>
       <c r="C42" s="8">
         <f t="shared" si="1"/>
-        <v>426.96615189799991</v>
+        <v>444.51327635749993</v>
       </c>
       <c r="D42" s="8">
         <f t="shared" si="2"/>
@@ -5628,7 +6003,7 @@
       </c>
       <c r="E42" s="8">
         <f t="shared" si="3"/>
-        <v>426.96615189799991</v>
+        <v>444.51327635749993</v>
       </c>
       <c r="F42" s="9">
         <v>25.636797481999999</v>
@@ -5740,8 +6115,18 @@
         <f t="shared" si="14"/>
         <v>18.986893032499999</v>
       </c>
+      <c r="AM42" s="9">
+        <v>17.547124459500004</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="9">
+        <f t="shared" si="15"/>
+        <v>17.547124459500004</v>
+      </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>97</v>
       </c>
@@ -5750,7 +6135,7 @@
       </c>
       <c r="C43" s="8">
         <f t="shared" si="1"/>
-        <v>2054.2886286634998</v>
+        <v>2181.8857489564998</v>
       </c>
       <c r="D43" s="8">
         <f t="shared" si="2"/>
@@ -5758,7 +6143,7 @@
       </c>
       <c r="E43" s="8">
         <f t="shared" si="3"/>
-        <v>2054.2886286634998</v>
+        <v>2181.8857489564998</v>
       </c>
       <c r="F43" s="9">
         <v>74.096976180999988</v>
@@ -5870,15 +6255,25 @@
         <f t="shared" si="14"/>
         <v>162.45318645399999</v>
       </c>
+      <c r="AM43" s="9">
+        <v>127.597120293</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="9">
+        <f t="shared" si="15"/>
+        <v>127.597120293</v>
+      </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C44" s="10">
         <f>SUM(C6:C43)</f>
-        <v>466468.70707493403</v>
+        <v>504017.10247343499</v>
       </c>
       <c r="D44" s="10">
         <f>SUM(D6:D43)</f>
@@ -5886,146 +6281,159 @@
       </c>
       <c r="E44" s="10">
         <f>SUM(E6:E43)</f>
-        <v>466468.70707493403</v>
+        <v>504017.10247343499</v>
       </c>
       <c r="F44" s="10">
-        <f t="shared" ref="F44:K44" si="15">SUM(F6:F43)</f>
+        <f t="shared" ref="F44:K44" si="16">SUM(F6:F43)</f>
         <v>47738.787757050995</v>
       </c>
       <c r="G44" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H44" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>47738.787757050995</v>
       </c>
       <c r="I44" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>38992.196601749994</v>
       </c>
       <c r="J44" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K44" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>38992.196601749994</v>
       </c>
       <c r="L44" s="10">
-        <f t="shared" ref="L44:N44" si="16">SUM(L6:L43)</f>
+        <f t="shared" ref="L44:N44" si="17">SUM(L6:L43)</f>
         <v>38074.18861744499</v>
       </c>
       <c r="M44" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N44" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>38074.18861744499</v>
       </c>
       <c r="O44" s="10">
-        <f t="shared" ref="O44:Q44" si="17">SUM(O6:O43)</f>
+        <f t="shared" ref="O44:Q44" si="18">SUM(O6:O43)</f>
         <v>42078.166217530998</v>
       </c>
       <c r="P44" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q44" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>42078.166217530998</v>
       </c>
       <c r="R44" s="10">
-        <f t="shared" ref="R44:T44" si="18">SUM(R6:R43)</f>
+        <f t="shared" ref="R44:T44" si="19">SUM(R6:R43)</f>
         <v>41694.38336779199</v>
       </c>
       <c r="S44" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="T44" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>41694.38336779199</v>
       </c>
       <c r="U44" s="10">
-        <f t="shared" ref="U44:W44" si="19">SUM(U6:U43)</f>
+        <f t="shared" ref="U44:W44" si="20">SUM(U6:U43)</f>
         <v>39126.580360400505</v>
       </c>
       <c r="V44" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W44" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>39126.580360400505</v>
       </c>
       <c r="X44" s="10">
-        <f t="shared" ref="X44:Z44" si="20">SUM(X6:X43)</f>
+        <f t="shared" ref="X44:Z44" si="21">SUM(X6:X43)</f>
         <v>49411.530814825986</v>
       </c>
       <c r="Y44" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Z44" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>49411.530814825986</v>
       </c>
       <c r="AA44" s="10">
-        <f t="shared" ref="AA44:AC44" si="21">SUM(AA6:AA43)</f>
+        <f t="shared" ref="AA44:AC44" si="22">SUM(AA6:AA43)</f>
         <v>44359.298597804009</v>
       </c>
       <c r="AB44" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="AC44" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>44359.298597804009</v>
       </c>
       <c r="AD44" s="10">
-        <f t="shared" ref="AD44:AF44" si="22">SUM(AD6:AD43)</f>
+        <f t="shared" ref="AD44:AF44" si="23">SUM(AD6:AD43)</f>
         <v>38216.300097394495</v>
       </c>
       <c r="AE44" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AF44" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>38216.300097394495</v>
       </c>
       <c r="AG44" s="10">
-        <f t="shared" ref="AG44:AI44" si="23">SUM(AG6:AG43)</f>
+        <f t="shared" ref="AG44:AI44" si="24">SUM(AG6:AG43)</f>
         <v>43913.952511930998</v>
       </c>
       <c r="AH44" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AI44" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>43913.952511930998</v>
       </c>
       <c r="AJ44" s="10">
-        <f t="shared" ref="AJ44:AL44" si="24">SUM(AJ6:AJ43)</f>
+        <f t="shared" ref="AJ44:AL44" si="25">SUM(AJ6:AJ43)</f>
         <v>42863.322131008994</v>
       </c>
       <c r="AK44" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AL44" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>42863.322131008994</v>
       </c>
+      <c r="AM44" s="10">
+        <f t="shared" ref="AM44:AO44" si="26">SUM(AM6:AM43)</f>
+        <v>37548.395398501008</v>
+      </c>
+      <c r="AN44" s="10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="AO44" s="10">
+        <f t="shared" si="26"/>
+        <v>37548.395398501008</v>
+      </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.3">
       <c r="X45" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="AM4:AO4"/>
     <mergeCell ref="AJ4:AL4"/>
     <mergeCell ref="AG4:AI4"/>
     <mergeCell ref="AD4:AF4"/>
